--- a/Stakeholdr_Map.xlsx
+++ b/Stakeholdr_Map.xlsx
@@ -31,12 +31,252 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="283">
   <si>
     <t>STAKEHOLDR</t>
   </si>
   <si>
-    <t>Categories &amp; audience types</t>
+    <t>Stakeholders exist in a public square where ideas are exchanged, your credibility is won or lost, and value is created, shared, or squandered.</t>
+  </si>
+  <si>
+    <t>How to plan for and engage stakeholders</t>
+  </si>
+  <si>
+    <t>PURPOSE</t>
+  </si>
+  <si>
+    <t>PLAN</t>
+  </si>
+  <si>
+    <t>EXECUTE</t>
+  </si>
+  <si>
+    <t>1. Set goals for your organization</t>
+  </si>
+  <si>
+    <t>5. Landscape analysis</t>
+  </si>
+  <si>
+    <t>9. Launch campaign</t>
+  </si>
+  <si>
+    <t>2. Issue identification</t>
+  </si>
+  <si>
+    <t>6. Cross-functional teams alignment</t>
+  </si>
+  <si>
+    <t>10. Ongoing stakeholder analysis</t>
+  </si>
+  <si>
+    <t>3. Stakeholder identification</t>
+  </si>
+  <si>
+    <t>7. Research and listening sessions</t>
+  </si>
+  <si>
+    <t>11. Collaborate with stakeholders</t>
+  </si>
+  <si>
+    <t>4. Stakeholder prioritization</t>
+  </si>
+  <si>
+    <t>8. Early stakeholder analysis and modeling</t>
+  </si>
+  <si>
+    <t>12. Realize shared value where possible</t>
+  </si>
+  <si>
+    <t>How to read the stakeholder map</t>
+  </si>
+  <si>
+    <t>X  Impact on the business:    Negative impact ◀ ▶ Positive impact</t>
+  </si>
+  <si>
+    <t>Y  Influence in the community:    Less influence ▼ ▲ Greater influence</t>
+  </si>
+  <si>
+    <t>Proactively Defend</t>
+  </si>
+  <si>
+    <t>Defend</t>
+  </si>
+  <si>
+    <t>Protect</t>
+  </si>
+  <si>
+    <t>Respond</t>
+  </si>
+  <si>
+    <t>Identify</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Maintain</t>
+  </si>
+  <si>
+    <t>Connect</t>
+  </si>
+  <si>
+    <t>Commit</t>
+  </si>
+  <si>
+    <t>Cooperate</t>
+  </si>
+  <si>
+    <t>Collaborate</t>
+  </si>
+  <si>
+    <t>Valuable Relationship</t>
+  </si>
+  <si>
+    <t>High Value Relationship</t>
+  </si>
+  <si>
+    <t>Strategic Partner</t>
+  </si>
+  <si>
+    <t>NEGATIVE IMPACT ON ORGANIZATION</t>
+  </si>
+  <si>
+    <t>THE WINNABLE MIDDLE</t>
+  </si>
+  <si>
+    <t>POSITIVE IMPACT ON ORGANIZATION</t>
+  </si>
+  <si>
+    <t>Defend license to operate</t>
+  </si>
+  <si>
+    <t>Dispel myths and misperceptions</t>
+  </si>
+  <si>
+    <t>Maximize shared value</t>
+  </si>
+  <si>
+    <t>Challenge misinformation</t>
+  </si>
+  <si>
+    <t>Appeal to their priorities</t>
+  </si>
+  <si>
+    <t>Maintain relationship</t>
+  </si>
+  <si>
+    <t>Plan for their influence in community</t>
+  </si>
+  <si>
+    <t>Identify shared value to move them our way</t>
+  </si>
+  <si>
+    <t>Champion their cause</t>
+  </si>
+  <si>
+    <t>Identify their reputation with audiences</t>
+  </si>
+  <si>
+    <t>Invest in relationship where possible</t>
+  </si>
+  <si>
+    <t>Recruit as public surrogates</t>
+  </si>
+  <si>
+    <t>“Influencer”</t>
+  </si>
+  <si>
+    <t>Identify our reputation with them</t>
+  </si>
+  <si>
+    <t>Communicate often</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>The 14 zones at a glance</t>
+  </si>
+  <si>
+    <t>Stakeholders are plotted on a two-axis grid: x measures impact on the business (do they work with you or against you?), y measures their influence in the community. The combination determines the relationship strategy.</t>
+  </si>
+  <si>
+    <t>← Works against you</t>
+  </si>
+  <si>
+    <t>↑ Greater community influence   ·   ↓ Less community influence</t>
+  </si>
+  <si>
+    <t>Works with you →</t>
+  </si>
+  <si>
+    <t>Strategy reference</t>
+  </si>
+  <si>
+    <t>For every zone, a stakeholder's position on the map returns a recommended posture and suggested immediate actions your team can take.</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Tone</t>
+  </si>
+  <si>
+    <t>Strategy and recommended action</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>Address Key Influencer. Launch plan to neutralize a major threat to the industry or company's license to operate; leverage reputation, resources, subject-matter experts, and other allied stakeholders to win. Measure and report on activity often.</t>
+  </si>
+  <si>
+    <t>Neutralize Threat. Defend license to operate. Defend reputation against regular attacks from stakeholders with high influence who are unlikely to move toward positive support; discredit message or position. Measure and report on activity often.</t>
+  </si>
+  <si>
+    <t>Mobilize Defense. Take action with internal resources and strategy. Defend reputation against regular attacks; manage expectations for changing stakeholder dynamic or group's influence in the community. Measure and report on activity regularly.</t>
+  </si>
+  <si>
+    <t>Challenge Stakeholder. Implement plan to challenge misinformation; reduce stakeholder's ability to destabilize the business or challenge brand identity and reputation.</t>
+  </si>
+  <si>
+    <t>React To Issues Or Conflict. Work to neutralize threat; educate stakeholder; resolve or minimize the stakeholder's ability or willingness to maintain conflict. Assign internal staff, team, or working group to execute response.</t>
+  </si>
+  <si>
+    <t>Winnable</t>
+  </si>
+  <si>
+    <t>Plan Ahead, Listen. Map stakeholder and plan to respond in the event of change; assign internal staff, team, or working group to execute plan if necessary.</t>
+  </si>
+  <si>
+    <t>Take Steps To Introduce Our Vision And Values. Take simple steps to engage; educate and create awareness about the business; look for ways to increase alignment and the stakeholder's influence over time.</t>
+  </si>
+  <si>
+    <t>Prioritize Resources Elsewhere. Take no action. Prioritize time and resources elsewhere but monitor for any negative changes in alignment or improved influence in the community over time.</t>
+  </si>
+  <si>
+    <t>Understand Needs, Work Towards Common Purpose. Build greater understanding between our company and stakeholder groups; look for opportunities to continue education and alignment that could lead to improved collaboration or affinity toward the business.</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Existing Alignment Produces Some Favorable Outcomes. Some value already exists and should continue with moderate level of commitment; maintain existing level of relationship.</t>
+  </si>
+  <si>
+    <t>Investing In Relationship Will Improve Our Business Or Reputation. Commitment important to our business; establish opportunities to work together and reap mutual benefits; leverage stakeholder's influence to increase our reputation.</t>
+  </si>
+  <si>
+    <t>Stakeholder Important To Our Business Success. Stakeholder is an important surrogate, ally, or business partner. Investing in and growing this relationship proactively supports and defends the business and increases our reputation. Prioritize collaboration and deploying engagement strategies.</t>
+  </si>
+  <si>
+    <t>Shared Value Introduced. Moderate shared value introduced; investing and growing this relationship produces value for our business and increases our reputation. Prioritize collaboration and engaging the stakeholder often to meet business and advocacy goals.</t>
+  </si>
+  <si>
+    <t>Shared Value Created. Shared value created. Formalize a working relationship or partnership with the stakeholder to produce and measure shared value; relationship grows the business, increases our reputation, and produces solutions.</t>
+  </si>
+  <si>
+    <t>Categories and audience types</t>
   </si>
   <si>
     <t>Communities</t>
@@ -231,232 +471,13 @@
     <t>US Senate</t>
   </si>
   <si>
-    <t>Stakeholders exist in a public square where ideas are exchanged, your credibility is won or lost, and value is created, shared, or squandered.</t>
-  </si>
-  <si>
-    <t>How to plan for and engage stakeholders</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>1. Set goals for your organization</t>
-  </si>
-  <si>
-    <t>5. Landscape analysis</t>
-  </si>
-  <si>
-    <t>9. Launch campaign</t>
-  </si>
-  <si>
-    <t>2. Issue identification</t>
-  </si>
-  <si>
-    <t>6. Cross-functional teams alignment</t>
-  </si>
-  <si>
-    <t>10. Ongoing stakeholder analysis</t>
-  </si>
-  <si>
-    <t>3. Stakeholder identification</t>
-  </si>
-  <si>
-    <t>7. Research &amp; listening sessions</t>
-  </si>
-  <si>
-    <t>11. Collaborate with stakeholders</t>
-  </si>
-  <si>
-    <t>4. Stakeholder prioritization</t>
-  </si>
-  <si>
-    <t>8. Early stakeholder analysis &amp; modeling</t>
-  </si>
-  <si>
-    <t>12. Realize shared value where possible</t>
-  </si>
-  <si>
-    <t>How to read the stakeholder map</t>
-  </si>
-  <si>
-    <t>X — Impact on the business:   Negative impact ◀ ▶ Positive impact</t>
-  </si>
-  <si>
-    <t>Y — Influence in the community:   Less influence ▼ ▲ Greater influence</t>
-  </si>
-  <si>
-    <t>Negative impact on organization</t>
-  </si>
-  <si>
-    <t>The winnable middle</t>
-  </si>
-  <si>
-    <t>Positive impact on organization</t>
-  </si>
-  <si>
-    <t>• Defend license to operate</t>
-  </si>
-  <si>
-    <t>• Dispel myths and misperceptions</t>
-  </si>
-  <si>
-    <t>• Maximize shared value</t>
-  </si>
-  <si>
-    <t>• Challenge misinformation</t>
-  </si>
-  <si>
-    <t>• Appeal to their priorities</t>
-  </si>
-  <si>
-    <t>• Maintain relationship</t>
-  </si>
-  <si>
-    <t>• Plan for their influence in community</t>
-  </si>
-  <si>
-    <t>• Identify shared value to move them our way</t>
-  </si>
-  <si>
-    <t>• Champion their cause</t>
-  </si>
-  <si>
-    <t>• Identify their reputation with audiences</t>
-  </si>
-  <si>
-    <t>• Invest in relationship where possible</t>
-  </si>
-  <si>
-    <t>• Recruit as public surrogates</t>
-  </si>
-  <si>
-    <t>• "Influencer"</t>
-  </si>
-  <si>
-    <t>• Identify our reputation with them</t>
-  </si>
-  <si>
-    <t>• Communicate often</t>
-  </si>
-  <si>
-    <t>Each zone: strategy &amp; recommended action</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Tone</t>
-  </si>
-  <si>
-    <t>Strategy — recommended action</t>
-  </si>
-  <si>
-    <t>Proactively Defend</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>Address Key Influencer — Launch plan to neutralize a major threat to the industry or company's license to operate; leverage reputation, resources, subject-matter experts, and other allied stakeholders to win. Measure and report on activity often.</t>
-  </si>
-  <si>
-    <t>Defend</t>
-  </si>
-  <si>
-    <t>Neutralize Threat — Defend license to operate. Defend reputation against regular attacks from stakeholders with high influence who are unlikely to move toward positive support; discredit message or position. Measure and report on activity often.</t>
-  </si>
-  <si>
-    <t>Protect</t>
-  </si>
-  <si>
-    <t>Mobilize Defense — Take action with internal resources and strategy. Defend reputation against regular attacks; manage expectations for changing stakeholder dynamic or group's influence in the community. Measure and report on activity regularly.</t>
-  </si>
-  <si>
-    <t>Respond</t>
-  </si>
-  <si>
-    <t>Challenge Stakeholder — Implement plan to challenge misinformation; reduce stakeholder's ability to destabilize the business or challenge brand identity and reputation.</t>
-  </si>
-  <si>
-    <t>Identify</t>
-  </si>
-  <si>
-    <t>React To Issues Or Conflict — Work to neutralize threat; educate stakeholder; resolve or minimize the stakeholder's ability or willingness to maintain conflict. Assign internal staff, team, or working group to execute response.</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>Winnable</t>
-  </si>
-  <si>
-    <t>Plan Ahead, Listen — Map stakeholder and plan to respond in the event of change; assign internal staff, team, or working group to execute plan if necessary.</t>
-  </si>
-  <si>
-    <t>Maintain</t>
-  </si>
-  <si>
-    <t>Take Steps To Introduce Our Vision And Values — Take simple steps to engage; educate and create awareness about the business; look for ways to increase alignment and the stakeholder's influence over time.</t>
-  </si>
-  <si>
-    <t>Connect</t>
-  </si>
-  <si>
-    <t>Prioritize Resources Elsewhere — Take no action. Prioritize time and resources elsewhere but monitor for any negative changes in alignment or improved influence in the community over time.</t>
-  </si>
-  <si>
-    <t>Commit</t>
-  </si>
-  <si>
-    <t>Understand Needs, Work Towards Common Purpose — Build greater understanding between our company and stakeholder groups; look for opportunities to continue education and alignment that could lead to improved collaboration or affinity toward the business.</t>
-  </si>
-  <si>
-    <t>Cooperate</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>Existing Alignment Produces Some Favorable Outcomes — Some value already exists and should continue with moderate level of commitment; maintain existing level of relationship.</t>
-  </si>
-  <si>
-    <t>Collaborate</t>
-  </si>
-  <si>
-    <t>Investing In Relationship Will Improve Our Business Or Reputation — Commitment important to our business; establish opportunities to work together and reap mutual benefits; leverage stakeholder's influence to increase our reputation.</t>
-  </si>
-  <si>
-    <t>Valuable Relationship</t>
-  </si>
-  <si>
-    <t>Stakeholder Important To Our Business Success — Stakeholder is an important surrogate, ally, or business partner. Investing in and growing this relationship proactively supports and defends the business and increases our reputation. Prioritize collaboration and deploying engagement strategies.</t>
-  </si>
-  <si>
-    <t>High Value Relationship</t>
-  </si>
-  <si>
-    <t>Shared Value Introduced — Moderate shared value introduced; investing and growing this relationship produces value for our business and increases our reputation. Prioritize collaboration and engaging the stakeholder often to meet business and advocacy goals.</t>
-  </si>
-  <si>
-    <t>Strategic Partner</t>
-  </si>
-  <si>
-    <t>Shared Value Created — Shared value created. Formalize a working relationship or partnership with the stakeholder to produce and measure shared value; relationship grows the business, increases our reputation, and produces solutions.</t>
-  </si>
-  <si>
     <t>How scores become coordinates</t>
   </si>
   <si>
-    <t>On the Scoring tab, every teammate rates each stakeholder on x and y from −10 to 10. Each teammate also has a weight. The final coordinate is the weighted average of their scores. A teammate with weight 1.5 counts 1.5 times more than one with weight 1.0.</t>
-  </si>
-  <si>
-    <t>final.x = Σ (member.x × member.weight) / Σ member.weight    |    final.y = Σ (member.y × member.weight) / Σ member.weight    |    zone = lookup(final.x, final.y)</t>
+    <t>On the Scoring tab, every teammate rates each stakeholder on x and y from minus 10 to 10. Each teammate also has a weight. The final coordinate is the weighted average of their scores. A teammate with weight 1.5 counts 1.5 times more than one with weight 1.0.</t>
+  </si>
+  <si>
+    <t>final.x = sum(member.x × member.weight) / sum(member.weight)      final.y = sum(member.y × member.weight) / sum(member.weight)      zone = lookup(final.x, final.y)</t>
   </si>
   <si>
     <t>#</t>
@@ -576,9 +597,6 @@
     <t>Cedarville Chamber</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -750,6 +768,9 @@
     <t>STAKEHOLDR MAP</t>
   </si>
   <si>
+    <t>Focus a stakeholder (Excel can't hover the map, so pick one here to isolate its zone and recommendation):</t>
+  </si>
+  <si>
     <t>IMPACT ON THE BUSINESS ▶</t>
   </si>
   <si>
@@ -789,40 +810,76 @@
     <t>y &lt; -5</t>
   </si>
   <si>
-    <t>← Works against you</t>
-  </si>
-  <si>
     <t>↑ Greater community influence  ·  ↓ Less community influence</t>
   </si>
   <si>
-    <t>Works with you →</t>
+    <t>Address Key Influencer: Launch plan to neutralize a major threat to the industry or company's license to operate; leverage reputation, resources, subject-matter experts, and other allied stakeholders to win. Measure and report on activity often.</t>
   </si>
   <si>
     <t>Canada</t>
   </si>
   <si>
+    <t>Neutralize Threat: Defend license to operate. Defend reputation against regular attacks from stakeholders with high influence who are unlikely to move toward positive support; discredit message or position. Measure and report on activity often.</t>
+  </si>
+  <si>
     <t>Mexico</t>
   </si>
   <si>
+    <t>Mobilize Defense: Take action with internal resources and strategy. Defend reputation against regular attacks; manage expectations for changing stakeholder dynamic or group's influence in the community. Measure and report on activity regularly.</t>
+  </si>
+  <si>
     <t>APJ</t>
   </si>
   <si>
     <t>Inactive</t>
   </si>
   <si>
+    <t>Challenge Stakeholder: Implement plan to challenge misinformation; reduce stakeholder's ability to destabilize the business or challenge brand identity and reputation.</t>
+  </si>
+  <si>
     <t>Other Countries</t>
   </si>
   <si>
+    <t>React To Issues Or Conflict: Work to neutralize threat; educate stakeholder; resolve or minimize the stakeholder's ability or willingness to maintain conflict. Assign internal staff, team, or working group to execute response.</t>
+  </si>
+  <si>
+    <t>Plan Ahead, Listen: Map stakeholder and plan to respond in the event of change; assign internal staff, team, or working group to execute plan if necessary.</t>
+  </si>
+  <si>
     <t>Middle East</t>
   </si>
   <si>
+    <t>Take Steps To Introduce Our Vision And Values: Take simple steps to engage; educate and create awareness about the business; look for ways to increase alignment and the stakeholder's influence over time.</t>
+  </si>
+  <si>
     <t>Africa</t>
   </si>
   <si>
+    <t>Prioritize Resources Elsewhere: Take no action. Prioritize time and resources elsewhere but monitor for any negative changes in alignment or improved influence in the community over time.</t>
+  </si>
+  <si>
     <t>Emerging APAC</t>
   </si>
   <si>
+    <t>Understand Needs, Work Towards Common Purpose: Build greater understanding between our company and stakeholder groups; look for opportunities to continue education and alignment that could lead to improved collaboration or affinity toward the business.</t>
+  </si>
+  <si>
     <t>Japan</t>
+  </si>
+  <si>
+    <t>Existing Alignment Produces Some Favorable Outcomes: Some value already exists and should continue with moderate level of commitment; maintain existing level of relationship.</t>
+  </si>
+  <si>
+    <t>Investing In Relationship Will Improve Our Business Or Reputation: Commitment important to our business; establish opportunities to work together and reap mutual benefits; leverage stakeholder's influence to increase our reputation.</t>
+  </si>
+  <si>
+    <t>Stakeholder Important To Our Business Success: Stakeholder is an important surrogate, ally, or business partner. Investing in and growing this relationship proactively supports and defends the business and increases our reputation. Prioritize collaboration and deploying engagement strategies.</t>
+  </si>
+  <si>
+    <t>Shared Value Introduced: Moderate shared value introduced; investing and growing this relationship produces value for our business and increases our reputation. Prioritize collaboration and engaging the stakeholder often to meet business and advocacy goals.</t>
+  </si>
+  <si>
+    <t>Shared Value Created: Shared value created. Formalize a working relationship or partnership with the stakeholder to produce and measure shared value; relationship grows the business, increases our reputation, and produces solutions.</t>
   </si>
 </sst>
 </file>
@@ -832,7 +889,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -843,18 +900,23 @@
     <font>
       <b/>
       <color rgb="FF3D3B39"/>
-      <sz val="24"/>
+      <sz val="28"/>
+      <name val="Newsreader"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666361"/>
+      <sz val="14"/>
+      <name val="Newsreader"/>
+    </font>
+    <font>
+      <color rgb="FF3D3B39"/>
+      <sz val="16"/>
       <name val="Newsreader"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF3D3B39"/>
-      <sz val="14"/>
-      <name val="Newsreader"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF3D3B39"/>
+      <color rgb="FF7A4A14"/>
       <sz val="11"/>
       <name val="Inter"/>
     </font>
@@ -864,14 +926,80 @@
       <name val="Inter"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF666361"/>
-      <sz val="13"/>
-      <name val="Newsreader"/>
+      <b/>
+      <color rgb="FF3D3B39"/>
+      <sz val="11"/>
+      <name val="Inter"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF666361"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF7A2424"/>
+      <sz val="9"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF7A4A14"/>
+      <sz val="9"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2F5A26"/>
+      <sz val="9"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB33C3C"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB07E1F"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF3E7A2E"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF7A2424"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2F5A26"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF7A4A14"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFABA9A4"/>
       <sz val="11"/>
       <name val="Inter"/>
     </font>
@@ -883,13 +1011,19 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFB33C3C"/>
+      <sz val="11"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF7A2424"/>
       <sz val="11"/>
       <name val="Inter"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF7A4A14"/>
+      <color rgb="FFB07E1F"/>
       <sz val="11"/>
       <name val="Inter"/>
     </font>
@@ -900,8 +1034,8 @@
       <name val="Inter"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FFABA9A4"/>
+      <b/>
+      <color rgb="FF3E7A2E"/>
       <sz val="11"/>
       <name val="Inter"/>
     </font>
@@ -919,12 +1053,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF666361"/>
+      <sz val="11"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFABA9A4"/>
       <sz val="11"/>
       <name val="Inter"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -933,42 +1073,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC2D9A4"/>
+        <fgColor rgb="FFE2A85F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF97C57A"/>
+        <fgColor rgb="FFF0C988"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4DBB0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1CF92"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE7C2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFBEBE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0EEE6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E4BD"/>
+        <fgColor rgb="FFF8E2B0"/>
       </patternFill>
     </fill>
     <fill>
@@ -983,12 +1098,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEFBEBE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4D6D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8E4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4DBB0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E4BD"/>
       </patternFill>
     </fill>
     <fill>
@@ -1003,6 +1133,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDDE7C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2D9A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1CF92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97C57A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF74B556"/>
       </patternFill>
     </fill>
@@ -1013,13 +1163,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0EEE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFB33C3C"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB33C3C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFB07E1F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB07E1F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF3E7A2E"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3E7A2E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFB33C3C"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFB07E1F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF3E7A2E"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -1035,6 +1250,15 @@
       <top style="thin">
         <color rgb="FFE8E6DE"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFE8E6DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFE8E6DE"/>
       </bottom>
@@ -1059,157 +1283,440 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="42">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD26A6A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A2424"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE29A9A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A2424"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFBEBE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A2424"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4D6D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A2424"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8E4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A4A14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4DBB0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A4A14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9E4BD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A4A14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCEFD1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7A4A14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFAEACA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2F5A26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDE7C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2F5A26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC2D9A4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2F5A26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB1CF92"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2F5A26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF97C57A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF74B556"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2423,753 +2930,942 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H62"/>
+  <dimension ref="B1:H85"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="38" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="3" ht="40" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G11" s="7"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="D18" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="E18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="F18" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="G18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="H18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="9" t="s">
+    </row>
+    <row r="19" ht="26" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="C19" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="D19" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="E19" s="19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+      <c r="F19" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="G19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="H19" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="9" t="s">
+    </row>
+    <row r="21" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="23" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+      <c r="C21" s="23"/>
+      <c r="D21" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E21" s="24"/>
+      <c r="F21" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="D22" s="27" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="F22" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="9" t="s">
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D23" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F23" s="28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D24" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="F24" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="9" t="s">
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="26" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="D25" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="F25" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="9" t="s">
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="26" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="D26" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="F26" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="9" t="s">
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="26" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
+      <c r="D27" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C38" s="44" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="D38" s="44"/>
+      <c r="E38" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="9" t="s">
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="46" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
+      <c r="C43" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="D43" s="46" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="46"/>
+    </row>
+    <row r="44" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="D44" s="49" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="22" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+    </row>
+    <row r="45" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+    </row>
+    <row r="46" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="49" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="11" t="s">
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="49"/>
+    </row>
+    <row r="47" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11" t="s">
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="49"/>
+    </row>
+    <row r="48" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11" t="s">
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+    </row>
+    <row r="49" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="11"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
+      <c r="D49" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12" t="s">
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+    </row>
+    <row r="50" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12" t="s">
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
+    </row>
+    <row r="51" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
+    </row>
+    <row r="52" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12" t="s">
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="49"/>
+    </row>
+    <row r="53" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12" t="s">
+      <c r="D53" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="12" t="s">
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
+      <c r="H53" s="49"/>
+    </row>
+    <row r="54" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12" t="s">
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+    </row>
+    <row r="55" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12" t="s">
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+    </row>
+    <row r="56" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+    </row>
+    <row r="57" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12" t="s">
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12" t="s">
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="C62" s="65" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="D62" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="E62" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="14" t="s">
+      <c r="F62" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15" t="s">
+      <c r="G62" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16" t="s">
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="G35" s="16"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
+      <c r="C63" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12" t="s">
+      <c r="D63" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12" t="s">
+      <c r="E63" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="12" t="s">
+      <c r="F63" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12" t="s">
+      <c r="G63" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12" t="s">
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
+      <c r="C64" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12" t="s">
+      <c r="D64" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12" t="s">
+      <c r="E64" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
+      <c r="F64" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12" t="s">
+      <c r="G64" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12" t="s">
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="12" t="s">
+      <c r="C65" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12" t="s">
+      <c r="D65" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12" t="s">
+      <c r="E65" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F41" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G41" s="12"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="F65" s="66" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="17" t="s">
+      <c r="G65" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="C44" s="17" t="s">
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="C66" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="18" t="s">
+      <c r="D66" s="66" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="E66" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="F66" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="19" t="s">
+      <c r="G66" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" s="12" t="s">
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="20" t="s">
+      <c r="C67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D47" s="12" t="s">
+      <c r="D67" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="21" t="s">
+      <c r="E67" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="12" t="s">
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="22" t="s">
+      <c r="C68" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D49" s="12" t="s">
+      <c r="D68" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="23" t="s">
+      <c r="E68" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="C50" s="9" t="s">
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="C69" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="24" t="s">
+      <c r="D69" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="12" t="s">
+      <c r="E69" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="25" t="s">
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B70" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" s="12" t="s">
+      <c r="C70" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="26" t="s">
+      <c r="D70" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D53" s="12" t="s">
+      <c r="E70" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="27" t="s">
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C71" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D71" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="28" t="s">
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" s="12" t="s">
+      <c r="C72" s="66" t="s">
         <v>132</v>
       </c>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="29" t="s">
+      <c r="D72" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D56" s="12" t="s">
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="66" t="s">
         <v>134</v>
       </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="30" t="s">
+      <c r="C73" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D57" s="12" t="s">
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="31" t="s">
+      <c r="C74" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D58" s="12" t="s">
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="C75" s="66" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="61" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="32" t="s">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-    </row>
-    <row r="62" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="33" t="s">
+      <c r="C76" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" s="66" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="66" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="66" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B81" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="83" ht="44" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+    </row>
+    <row r="85" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B85" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="C85" s="67"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
+      <c r="H85" s="67"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
+  <mergeCells count="48">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="D43:H43"/>
     <mergeCell ref="D44:H44"/>
     <mergeCell ref="D45:H45"/>
     <mergeCell ref="D46:H46"/>
@@ -3184,9 +3880,10 @@
     <mergeCell ref="D55:H55"/>
     <mergeCell ref="D56:H56"/>
     <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B83:H83"/>
+    <mergeCell ref="B85:H85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3205,106 +3902,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34" t="s">
+      <c r="A1" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="B1" s="68" t="s">
         <v>150</v>
       </c>
+      <c r="C1" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="N1" s="68" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="36">
+      <c r="B2" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="69">
         <v>1.5</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36">
+      <c r="D2" s="69"/>
+      <c r="E2" s="69">
         <v>1.2</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69">
         <v>1</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36">
+      <c r="H2" s="69"/>
+      <c r="I2" s="69">
         <v>0.8</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36">
+      <c r="J2" s="69"/>
+      <c r="K2" s="69">
         <v>0.7</v>
       </c>
-      <c r="L2" s="36"/>
-      <c r="M2" s="35" t="s">
-        <v>152</v>
+      <c r="L2" s="69"/>
+      <c r="M2" s="43" t="s">
+        <v>159</v>
       </c>
       <c r="N2">
         <f>=C2+E2+G2+I2+K2</f>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="L3" s="34" t="s">
-        <v>155</v>
+      <c r="A3" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="K3" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="L3" s="68" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -4359,7 +5056,7 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="12" max="13" width="7" style="37" customWidth="1"/>
+    <col min="12" max="13" width="7" style="70" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="40" customWidth="1"/>
@@ -4368,59 +5065,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="38" t="s">
+      <c r="A1" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="C1" s="71" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="71" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" s="71" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="71" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="71" t="s">
+        <v>170</v>
+      </c>
+      <c r="K1" s="71" t="s">
+        <v>171</v>
+      </c>
+      <c r="L1" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="M1" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="K1" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="N1" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="O1" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="P1" s="38" t="s">
-        <v>167</v>
+      <c r="N1" s="71" t="s">
+        <v>172</v>
+      </c>
+      <c r="O1" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="P1" s="71" t="s">
+        <v>174</v>
       </c>
       <c r="Q1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="R1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -4428,49 +5125,49 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="K2" t="s">
-        <v>177</v>
-      </c>
-      <c r="L2" s="37">
+        <v>184</v>
+      </c>
+      <c r="L2" s="70">
         <f>=IF(B2="","",Scoring!M4)</f>
       </c>
-      <c r="M2" s="37">
+      <c r="M2" s="70">
         <f>=IF(B2="","",Scoring!N4)</f>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="73">
         <f>=IF(B2="","",INDEX(ZoneGrid,R2,Q2))</f>
       </c>
       <c r="O2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="Q2">
         <f>=IF(B2="","",IF(L2&lt;-5,1,IF(L2&lt;0,2,IF(L2&lt;5,3,4))))</f>
@@ -4484,49 +5181,49 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G3" t="s">
         <v>180</v>
       </c>
-      <c r="C3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G3" t="s">
-        <v>173</v>
-      </c>
       <c r="H3" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I3" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J3" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L3" s="37">
+        <v>188</v>
+      </c>
+      <c r="L3" s="70">
         <f>=IF(B3="","",Scoring!M5)</f>
       </c>
-      <c r="M3" s="37">
+      <c r="M3" s="70">
         <f>=IF(B3="","",Scoring!N5)</f>
       </c>
-      <c r="N3" s="41">
+      <c r="N3" s="74">
         <f>=IF(B3="","",INDEX(ZoneGrid,R3,Q3))</f>
       </c>
       <c r="O3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <f>=IF(B3="","",IF(L3&lt;-5,1,IF(L3&lt;0,2,IF(L3&lt;5,3,4))))</f>
@@ -4540,49 +5237,49 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" t="s">
         <v>184</v>
       </c>
-      <c r="C4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I4" t="s">
-        <v>181</v>
-      </c>
-      <c r="J4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K4" t="s">
-        <v>177</v>
-      </c>
-      <c r="L4" s="37">
+      <c r="L4" s="70">
         <f>=IF(B4="","",Scoring!M6)</f>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="70">
         <f>=IF(B4="","",Scoring!N6)</f>
       </c>
-      <c r="N4" s="42">
+      <c r="N4" s="75">
         <f>=IF(B4="","",INDEX(ZoneGrid,R4,Q4))</f>
       </c>
       <c r="O4" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="Q4">
         <f>=IF(B4="","",IF(L4&lt;-5,1,IF(L4&lt;0,2,IF(L4&lt;5,3,4))))</f>
@@ -4596,49 +5293,49 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L5" s="37">
+        <v>184</v>
+      </c>
+      <c r="L5" s="70">
         <f>=IF(B5="","",Scoring!M7)</f>
       </c>
-      <c r="M5" s="37">
+      <c r="M5" s="70">
         <f>=IF(B5="","",Scoring!N7)</f>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="73">
         <f>=IF(B5="","",INDEX(ZoneGrid,R5,Q5))</f>
       </c>
       <c r="O5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="Q5">
         <f>=IF(B5="","",IF(L5&lt;-5,1,IF(L5&lt;0,2,IF(L5&lt;5,3,4))))</f>
@@ -4652,49 +5349,49 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G6" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="I6" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J6" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>177</v>
-      </c>
-      <c r="L6" s="37">
+        <v>184</v>
+      </c>
+      <c r="L6" s="70">
         <f>=IF(B6="","",Scoring!M8)</f>
       </c>
-      <c r="M6" s="37">
+      <c r="M6" s="70">
         <f>=IF(B6="","",Scoring!N8)</f>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="76">
         <f>=IF(B6="","",INDEX(ZoneGrid,R6,Q6))</f>
       </c>
       <c r="O6" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q6">
         <f>=IF(B6="","",IF(L6&lt;-5,1,IF(L6&lt;0,2,IF(L6&lt;5,3,4))))</f>
@@ -4708,49 +5405,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F7" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I7" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J7" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>177</v>
-      </c>
-      <c r="L7" s="37">
+        <v>184</v>
+      </c>
+      <c r="L7" s="70">
         <f>=IF(B7="","",Scoring!M9)</f>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="70">
         <f>=IF(B7="","",Scoring!N9)</f>
       </c>
-      <c r="N7" s="44">
+      <c r="N7" s="77">
         <f>=IF(B7="","",INDEX(ZoneGrid,R7,Q7))</f>
       </c>
       <c r="O7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q7">
         <f>=IF(B7="","",IF(L7&lt;-5,1,IF(L7&lt;0,2,IF(L7&lt;5,3,4))))</f>
@@ -4764,49 +5461,49 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G8" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I8" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J8" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K8" t="s">
-        <v>177</v>
-      </c>
-      <c r="L8" s="37">
+        <v>184</v>
+      </c>
+      <c r="L8" s="70">
         <f>=IF(B8="","",Scoring!M10)</f>
       </c>
-      <c r="M8" s="37">
+      <c r="M8" s="70">
         <f>=IF(B8="","",Scoring!N10)</f>
       </c>
-      <c r="N8" s="42">
+      <c r="N8" s="75">
         <f>=IF(B8="","",INDEX(ZoneGrid,R8,Q8))</f>
       </c>
       <c r="O8" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q8">
         <f>=IF(B8="","",IF(L8&lt;-5,1,IF(L8&lt;0,2,IF(L8&lt;5,3,4))))</f>
@@ -4820,49 +5517,49 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G9" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H9" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
-      </c>
-      <c r="L9" s="37">
+        <v>188</v>
+      </c>
+      <c r="L9" s="70">
         <f>=IF(B9="","",Scoring!M11)</f>
       </c>
-      <c r="M9" s="37">
+      <c r="M9" s="70">
         <f>=IF(B9="","",Scoring!N11)</f>
       </c>
-      <c r="N9" s="45">
+      <c r="N9" s="78">
         <f>=IF(B9="","",INDEX(ZoneGrid,R9,Q9))</f>
       </c>
       <c r="O9" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P9" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q9">
         <f>=IF(B9="","",IF(L9&lt;-5,1,IF(L9&lt;0,2,IF(L9&lt;5,3,4))))</f>
@@ -4876,49 +5573,49 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G10" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I10" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J10" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K10" t="s">
-        <v>204</v>
-      </c>
-      <c r="L10" s="37">
+        <v>210</v>
+      </c>
+      <c r="L10" s="70">
         <f>=IF(B10="","",Scoring!M12)</f>
       </c>
-      <c r="M10" s="37">
+      <c r="M10" s="70">
         <f>=IF(B10="","",Scoring!N12)</f>
       </c>
-      <c r="N10" s="46">
+      <c r="N10" s="79">
         <f>=IF(B10="","",INDEX(ZoneGrid,R10,Q10))</f>
       </c>
       <c r="O10" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P10" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q10">
         <f>=IF(B10="","",IF(L10&lt;-5,1,IF(L10&lt;0,2,IF(L10&lt;5,3,4))))</f>
@@ -4932,49 +5629,49 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="F11" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G11" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I11" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J11" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K11" t="s">
-        <v>182</v>
-      </c>
-      <c r="L11" s="37">
+        <v>188</v>
+      </c>
+      <c r="L11" s="70">
         <f>=IF(B11="","",Scoring!M13)</f>
       </c>
-      <c r="M11" s="37">
+      <c r="M11" s="70">
         <f>=IF(B11="","",Scoring!N13)</f>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="78">
         <f>=IF(B11="","",INDEX(ZoneGrid,R11,Q11))</f>
       </c>
       <c r="O11" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <f>=IF(B11="","",IF(L11&lt;-5,1,IF(L11&lt;0,2,IF(L11&lt;5,3,4))))</f>
@@ -4988,49 +5685,49 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G12" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I12" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J12" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
-        <v>177</v>
-      </c>
-      <c r="L12" s="37">
+        <v>184</v>
+      </c>
+      <c r="L12" s="70">
         <f>=IF(B12="","",Scoring!M14)</f>
       </c>
-      <c r="M12" s="37">
+      <c r="M12" s="70">
         <f>=IF(B12="","",Scoring!N14)</f>
       </c>
-      <c r="N12" s="43">
+      <c r="N12" s="76">
         <f>=IF(B12="","",INDEX(ZoneGrid,R12,Q12))</f>
       </c>
       <c r="O12" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <f>=IF(B12="","",IF(L12&lt;-5,1,IF(L12&lt;0,2,IF(L12&lt;5,3,4))))</f>
@@ -5044,49 +5741,49 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C13" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G13" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H13" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I13" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>177</v>
-      </c>
-      <c r="L13" s="37">
+        <v>184</v>
+      </c>
+      <c r="L13" s="70">
         <f>=IF(B13="","",Scoring!M15)</f>
       </c>
-      <c r="M13" s="37">
+      <c r="M13" s="70">
         <f>=IF(B13="","",Scoring!N15)</f>
       </c>
-      <c r="N13" s="44">
+      <c r="N13" s="77">
         <f>=IF(B13="","",INDEX(ZoneGrid,R13,Q13))</f>
       </c>
       <c r="O13" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P13" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q13">
         <f>=IF(B13="","",IF(L13&lt;-5,1,IF(L13&lt;0,2,IF(L13&lt;5,3,4))))</f>
@@ -5100,49 +5797,49 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G14" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I14" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K14" t="s">
-        <v>182</v>
-      </c>
-      <c r="L14" s="37">
+        <v>188</v>
+      </c>
+      <c r="L14" s="70">
         <f>=IF(B14="","",Scoring!M16)</f>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="70">
         <f>=IF(B14="","",Scoring!N16)</f>
       </c>
-      <c r="N14" s="45">
+      <c r="N14" s="78">
         <f>=IF(B14="","",INDEX(ZoneGrid,R14,Q14))</f>
       </c>
       <c r="O14" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q14">
         <f>=IF(B14="","",IF(L14&lt;-5,1,IF(L14&lt;0,2,IF(L14&lt;5,3,4))))</f>
@@ -5156,49 +5853,49 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G15" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I15" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K15" t="s">
-        <v>177</v>
-      </c>
-      <c r="L15" s="37">
+        <v>184</v>
+      </c>
+      <c r="L15" s="70">
         <f>=IF(B15="","",Scoring!M17)</f>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="70">
         <f>=IF(B15="","",Scoring!N17)</f>
       </c>
-      <c r="N15" s="43">
+      <c r="N15" s="76">
         <f>=IF(B15="","",INDEX(ZoneGrid,R15,Q15))</f>
       </c>
       <c r="O15" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <f>=IF(B15="","",IF(L15&lt;-5,1,IF(L15&lt;0,2,IF(L15&lt;5,3,4))))</f>
@@ -5212,49 +5909,49 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D16" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H16" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="I16" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J16" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
-        <v>177</v>
-      </c>
-      <c r="L16" s="37">
+        <v>184</v>
+      </c>
+      <c r="L16" s="70">
         <f>=IF(B16="","",Scoring!M18)</f>
       </c>
-      <c r="M16" s="37">
+      <c r="M16" s="70">
         <f>=IF(B16="","",Scoring!N18)</f>
       </c>
-      <c r="N16" s="40">
+      <c r="N16" s="73">
         <f>=IF(B16="","",INDEX(ZoneGrid,R16,Q16))</f>
       </c>
       <c r="O16" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q16">
         <f>=IF(B16="","",IF(L16&lt;-5,1,IF(L16&lt;0,2,IF(L16&lt;5,3,4))))</f>
@@ -5268,49 +5965,49 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D17" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G17" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H17" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="I17" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="J17" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K17" t="s">
-        <v>182</v>
-      </c>
-      <c r="L17" s="37">
+        <v>188</v>
+      </c>
+      <c r="L17" s="70">
         <f>=IF(B17="","",Scoring!M19)</f>
       </c>
-      <c r="M17" s="37">
+      <c r="M17" s="70">
         <f>=IF(B17="","",Scoring!N19)</f>
       </c>
-      <c r="N17" s="40">
+      <c r="N17" s="73">
         <f>=IF(B17="","",INDEX(ZoneGrid,R17,Q17))</f>
       </c>
       <c r="O17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q17">
         <f>=IF(B17="","",IF(L17&lt;-5,1,IF(L17&lt;0,2,IF(L17&lt;5,3,4))))</f>
@@ -5324,49 +6021,49 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="F18" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G18" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H18" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I18" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K18" t="s">
-        <v>177</v>
-      </c>
-      <c r="L18" s="37">
+        <v>184</v>
+      </c>
+      <c r="L18" s="70">
         <f>=IF(B18="","",Scoring!M20)</f>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="70">
         <f>=IF(B18="","",Scoring!N20)</f>
       </c>
-      <c r="N18" s="42">
+      <c r="N18" s="75">
         <f>=IF(B18="","",INDEX(ZoneGrid,R18,Q18))</f>
       </c>
       <c r="O18" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P18" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q18">
         <f>=IF(B18="","",IF(L18&lt;-5,1,IF(L18&lt;0,2,IF(L18&lt;5,3,4))))</f>
@@ -5380,49 +6077,49 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D19" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="F19" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G19" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H19" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I19" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J19" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K19" t="s">
-        <v>182</v>
-      </c>
-      <c r="L19" s="37">
+        <v>188</v>
+      </c>
+      <c r="L19" s="70">
         <f>=IF(B19="","",Scoring!M21)</f>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="70">
         <f>=IF(B19="","",Scoring!N21)</f>
       </c>
-      <c r="N19" s="47">
+      <c r="N19" s="80">
         <f>=IF(B19="","",INDEX(ZoneGrid,R19,Q19))</f>
       </c>
       <c r="O19" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q19">
         <f>=IF(B19="","",IF(L19&lt;-5,1,IF(L19&lt;0,2,IF(L19&lt;5,3,4))))</f>
@@ -5436,49 +6133,49 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D20" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G20" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H20" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I20" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J20" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K20" t="s">
-        <v>177</v>
-      </c>
-      <c r="L20" s="37">
+        <v>184</v>
+      </c>
+      <c r="L20" s="70">
         <f>=IF(B20="","",Scoring!M22)</f>
       </c>
-      <c r="M20" s="37">
+      <c r="M20" s="70">
         <f>=IF(B20="","",Scoring!N22)</f>
       </c>
-      <c r="N20" s="43">
+      <c r="N20" s="76">
         <f>=IF(B20="","",INDEX(ZoneGrid,R20,Q20))</f>
       </c>
       <c r="O20" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q20">
         <f>=IF(B20="","",IF(L20&lt;-5,1,IF(L20&lt;0,2,IF(L20&lt;5,3,4))))</f>
@@ -5492,49 +6189,49 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="F21" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G21" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H21" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I21" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="J21" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K21" t="s">
-        <v>182</v>
-      </c>
-      <c r="L21" s="37">
+        <v>188</v>
+      </c>
+      <c r="L21" s="70">
         <f>=IF(B21="","",Scoring!M23)</f>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="70">
         <f>=IF(B21="","",Scoring!N23)</f>
       </c>
-      <c r="N21" s="45">
+      <c r="N21" s="78">
         <f>=IF(B21="","",INDEX(ZoneGrid,R21,Q21))</f>
       </c>
       <c r="O21" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P21" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q21">
         <f>=IF(B21="","",IF(L21&lt;-5,1,IF(L21&lt;0,2,IF(L21&lt;5,3,4))))</f>
@@ -5547,10 +6244,10 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="70">
         <f>=IF(B22="","",Scoring!M24)</f>
       </c>
-      <c r="M22" s="37">
+      <c r="M22" s="70">
         <f>=IF(B22="","",Scoring!N24)</f>
       </c>
       <c r="N22">
@@ -5567,10 +6264,10 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="L23" s="37">
+      <c r="L23" s="70">
         <f>=IF(B23="","",Scoring!M25)</f>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="70">
         <f>=IF(B23="","",Scoring!N25)</f>
       </c>
       <c r="N23">
@@ -5587,10 +6284,10 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="L24" s="37">
+      <c r="L24" s="70">
         <f>=IF(B24="","",Scoring!M26)</f>
       </c>
-      <c r="M24" s="37">
+      <c r="M24" s="70">
         <f>=IF(B24="","",Scoring!N26)</f>
       </c>
       <c r="N24">
@@ -5607,10 +6304,10 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="70">
         <f>=IF(B25="","",Scoring!M27)</f>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="70">
         <f>=IF(B25="","",Scoring!N27)</f>
       </c>
       <c r="N25">
@@ -5627,10 +6324,10 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="L26" s="37">
+      <c r="L26" s="70">
         <f>=IF(B26="","",Scoring!M28)</f>
       </c>
-      <c r="M26" s="37">
+      <c r="M26" s="70">
         <f>=IF(B26="","",Scoring!N28)</f>
       </c>
       <c r="N26">
@@ -5647,10 +6344,10 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="L27" s="37">
+      <c r="L27" s="70">
         <f>=IF(B27="","",Scoring!M29)</f>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="70">
         <f>=IF(B27="","",Scoring!N29)</f>
       </c>
       <c r="N27">
@@ -5667,10 +6364,10 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="L28" s="37">
+      <c r="L28" s="70">
         <f>=IF(B28="","",Scoring!M30)</f>
       </c>
-      <c r="M28" s="37">
+      <c r="M28" s="70">
         <f>=IF(B28="","",Scoring!N30)</f>
       </c>
       <c r="N28">
@@ -5687,10 +6384,10 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="L29" s="37">
+      <c r="L29" s="70">
         <f>=IF(B29="","",Scoring!M31)</f>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="70">
         <f>=IF(B29="","",Scoring!N31)</f>
       </c>
       <c r="N29">
@@ -5707,10 +6404,10 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="L30" s="37">
+      <c r="L30" s="70">
         <f>=IF(B30="","",Scoring!M32)</f>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="70">
         <f>=IF(B30="","",Scoring!N32)</f>
       </c>
       <c r="N30">
@@ -5727,10 +6424,10 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="70">
         <f>=IF(B31="","",Scoring!M33)</f>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="70">
         <f>=IF(B31="","",Scoring!N33)</f>
       </c>
       <c r="N31">
@@ -5935,74 +6632,101 @@
     <col min="12" max="12" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C3" s="49" t="s">
-        <v>239</v>
-      </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
+    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1" s="82" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+    </row>
+    <row r="2" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H2" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="83"/>
+      <c r="J2" s="84">
+        <f>=IFERROR("x "&amp;TEXT(INDEX(Workspace!$L$2:$L$31,MATCH($H$2,Workspace!$B$2:$B$31,0)),"0.0")&amp;"     y "&amp;TEXT(INDEX(Workspace!$M$2:$M$31,MATCH($H$2,Workspace!$B$2:$B$31,0)),"0.0"),"")</f>
+      </c>
+      <c r="K2" s="84"/>
+      <c r="L2" s="85">
+        <f>=IFERROR(INDEX(Workspace!$N$2:$N$31,MATCH($H$2,Workspace!$B$2:$B$31,0)),"")</f>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C3" s="86" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="H3" s="7">
+        <f>=IFERROR("Recommendation:  "&amp;VLOOKUP(INDEX(Workspace!$N$2:$N$31,MATCH($H$2,Workspace!$B$2:$B$31,0)),RecTable,2,FALSE),"")</f>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>246</v>
-      </c>
-      <c r="C5" s="53">
+      <c r="C4" s="87" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="87" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="87" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" s="87" t="s">
+        <v>250</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="J4" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="K4" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="L4" s="46" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="90">
         <f>="Proactively Defend"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="91">
         <f>="Defend"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="92">
         <f>="Valuable Relationship"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="93">
         <f>="Strategic Partner"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=1),Workspace!$B$2:$B$31,"")))</f>
       </c>
       <c r="H5">
         <f>=IF(Workspace!B2="","",Workspace!B2)</f>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="70">
         <f>=IF(Workspace!B2="","",Workspace!L2)</f>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="70">
         <f>=IF(Workspace!B2="","",Workspace!M2)</f>
       </c>
       <c r="K5">
@@ -6012,30 +6736,30 @@
         <f>=IF(Workspace!B2="","",VLOOKUP(Workspace!N2,RecTable,2,FALSE))</f>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="54">
+    <row r="6" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="88"/>
+      <c r="B6" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="91">
         <f>="Defend"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="94">
         <f>="Protect"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="95">
         <f>="Collaborate"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="96">
         <f>="High Value Relationship"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=2),Workspace!$B$2:$B$31,"")))</f>
       </c>
       <c r="H6">
         <f>=IF(Workspace!B3="","",Workspace!B3)</f>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="70">
         <f>=IF(Workspace!B3="","",Workspace!L3)</f>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="70">
         <f>=IF(Workspace!B3="","",Workspace!M3)</f>
       </c>
       <c r="K6">
@@ -6045,30 +6769,30 @@
         <f>=IF(Workspace!B3="","",VLOOKUP(Workspace!N3,RecTable,2,FALSE))</f>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="57">
+    <row r="7" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="88"/>
+      <c r="B7" s="89" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="94">
         <f>="Protect"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="97">
         <f>="Respond"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="98">
         <f>="Cooperate"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="95">
         <f>="Collaborate"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=3),Workspace!$B$2:$B$31,"")))</f>
       </c>
       <c r="H7">
         <f>=IF(Workspace!B4="","",Workspace!B4)</f>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="70">
         <f>=IF(Workspace!B4="","",Workspace!L4)</f>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="70">
         <f>=IF(Workspace!B4="","",Workspace!M4)</f>
       </c>
       <c r="K7">
@@ -6078,30 +6802,30 @@
         <f>=IF(Workspace!B4="","",VLOOKUP(Workspace!N4,RecTable,2,FALSE))</f>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="57">
+    <row r="8" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="88"/>
+      <c r="B8" s="89" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="94">
         <f>="Protect"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="97">
         <f>="Respond"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="98">
         <f>="Cooperate"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="95">
         <f>="Collaborate"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=4),Workspace!$B$2:$B$31,"")))</f>
       </c>
       <c r="H8">
         <f>=IF(Workspace!B5="","",Workspace!B5)</f>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="70">
         <f>=IF(Workspace!B5="","",Workspace!L5)</f>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="70">
         <f>=IF(Workspace!B5="","",Workspace!M5)</f>
       </c>
       <c r="K8">
@@ -6111,30 +6835,30 @@
         <f>=IF(Workspace!B5="","",VLOOKUP(Workspace!N5,RecTable,2,FALSE))</f>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="62">
+    <row r="9" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="88"/>
+      <c r="B9" s="89" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="99">
         <f>="Identify"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="99">
         <f>="Identify"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="100">
         <f>="Commit"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="F9" s="63">
+      <c r="F9" s="100">
         <f>="Commit"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=5),Workspace!$B$2:$B$31,"")))</f>
       </c>
       <c r="H9">
         <f>=IF(Workspace!B6="","",Workspace!B6)</f>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="70">
         <f>=IF(Workspace!B6="","",Workspace!L6)</f>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="70">
         <f>=IF(Workspace!B6="","",Workspace!M6)</f>
       </c>
       <c r="K9">
@@ -6144,30 +6868,30 @@
         <f>=IF(Workspace!B6="","",VLOOKUP(Workspace!N6,RecTable,2,FALSE))</f>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="64">
+    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="88"/>
+      <c r="B10" s="89" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="101">
         <f>="Monitor"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=1)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="101">
         <f>="Monitor"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=2)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="102">
         <f>="Maintain"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=3)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,"")))</f>
       </c>
-      <c r="F10" s="66">
+      <c r="F10" s="103">
         <f>="Connect"&amp;IF(TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,""))="","",CHAR(10)&amp;TEXTJOIN(CHAR(10),TRUE,IF((Workspace!$Q$2:$Q$31=4)*(Workspace!$R$2:$R$31=6),Workspace!$B$2:$B$31,"")))</f>
       </c>
       <c r="H10">
         <f>=IF(Workspace!B7="","",Workspace!B7)</f>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="70">
         <f>=IF(Workspace!B7="","",Workspace!L7)</f>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="70">
         <f>=IF(Workspace!B7="","",Workspace!M7)</f>
       </c>
       <c r="K10">
@@ -6181,10 +6905,10 @@
       <c r="H11">
         <f>=IF(Workspace!B8="","",Workspace!B8)</f>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="70">
         <f>=IF(Workspace!B8="","",Workspace!L8)</f>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="70">
         <f>=IF(Workspace!B8="","",Workspace!M8)</f>
       </c>
       <c r="K11">
@@ -6195,23 +6919,23 @@
       </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="67" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="67"/>
-      <c r="F12" s="68" t="s">
-        <v>254</v>
+      <c r="C12" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45" t="s">
+        <v>58</v>
       </c>
       <c r="H12">
         <f>=IF(Workspace!B9="","",Workspace!B9)</f>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="70">
         <f>=IF(Workspace!B9="","",Workspace!L9)</f>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="70">
         <f>=IF(Workspace!B9="","",Workspace!M9)</f>
       </c>
       <c r="K12">
@@ -6225,10 +6949,10 @@
       <c r="H13">
         <f>=IF(Workspace!B10="","",Workspace!B10)</f>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="70">
         <f>=IF(Workspace!B10="","",Workspace!L10)</f>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="70">
         <f>=IF(Workspace!B10="","",Workspace!M10)</f>
       </c>
       <c r="K13">
@@ -6242,10 +6966,10 @@
       <c r="H14">
         <f>=IF(Workspace!B11="","",Workspace!B11)</f>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="70">
         <f>=IF(Workspace!B11="","",Workspace!L11)</f>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="70">
         <f>=IF(Workspace!B11="","",Workspace!M11)</f>
       </c>
       <c r="K14">
@@ -6259,10 +6983,10 @@
       <c r="H15">
         <f>=IF(Workspace!B12="","",Workspace!B12)</f>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="70">
         <f>=IF(Workspace!B12="","",Workspace!L12)</f>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="70">
         <f>=IF(Workspace!B12="","",Workspace!M12)</f>
       </c>
       <c r="K15">
@@ -6276,10 +7000,10 @@
       <c r="H16">
         <f>=IF(Workspace!B13="","",Workspace!B13)</f>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="70">
         <f>=IF(Workspace!B13="","",Workspace!L13)</f>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="70">
         <f>=IF(Workspace!B13="","",Workspace!M13)</f>
       </c>
       <c r="K16">
@@ -6293,10 +7017,10 @@
       <c r="H17">
         <f>=IF(Workspace!B14="","",Workspace!B14)</f>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="70">
         <f>=IF(Workspace!B14="","",Workspace!L14)</f>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="70">
         <f>=IF(Workspace!B14="","",Workspace!M14)</f>
       </c>
       <c r="K17">
@@ -6310,10 +7034,10 @@
       <c r="H18">
         <f>=IF(Workspace!B15="","",Workspace!B15)</f>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="70">
         <f>=IF(Workspace!B15="","",Workspace!L15)</f>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="70">
         <f>=IF(Workspace!B15="","",Workspace!M15)</f>
       </c>
       <c r="K18">
@@ -6327,10 +7051,10 @@
       <c r="H19">
         <f>=IF(Workspace!B16="","",Workspace!B16)</f>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="70">
         <f>=IF(Workspace!B16="","",Workspace!L16)</f>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="70">
         <f>=IF(Workspace!B16="","",Workspace!M16)</f>
       </c>
       <c r="K19">
@@ -6344,10 +7068,10 @@
       <c r="H20">
         <f>=IF(Workspace!B17="","",Workspace!B17)</f>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="70">
         <f>=IF(Workspace!B17="","",Workspace!L17)</f>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="70">
         <f>=IF(Workspace!B17="","",Workspace!M17)</f>
       </c>
       <c r="K20">
@@ -6361,10 +7085,10 @@
       <c r="H21">
         <f>=IF(Workspace!B18="","",Workspace!B18)</f>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="70">
         <f>=IF(Workspace!B18="","",Workspace!L18)</f>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="70">
         <f>=IF(Workspace!B18="","",Workspace!M18)</f>
       </c>
       <c r="K21">
@@ -6378,10 +7102,10 @@
       <c r="H22">
         <f>=IF(Workspace!B19="","",Workspace!B19)</f>
       </c>
-      <c r="I22" s="37">
+      <c r="I22" s="70">
         <f>=IF(Workspace!B19="","",Workspace!L19)</f>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="70">
         <f>=IF(Workspace!B19="","",Workspace!M19)</f>
       </c>
       <c r="K22">
@@ -6395,10 +7119,10 @@
       <c r="H23">
         <f>=IF(Workspace!B20="","",Workspace!B20)</f>
       </c>
-      <c r="I23" s="37">
+      <c r="I23" s="70">
         <f>=IF(Workspace!B20="","",Workspace!L20)</f>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="70">
         <f>=IF(Workspace!B20="","",Workspace!M20)</f>
       </c>
       <c r="K23">
@@ -6412,10 +7136,10 @@
       <c r="H24">
         <f>=IF(Workspace!B21="","",Workspace!B21)</f>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="70">
         <f>=IF(Workspace!B21="","",Workspace!L21)</f>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="70">
         <f>=IF(Workspace!B21="","",Workspace!M21)</f>
       </c>
       <c r="K24">
@@ -6429,10 +7153,10 @@
       <c r="H25">
         <f>=IF(Workspace!B22="","",Workspace!B22)</f>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="70">
         <f>=IF(Workspace!B22="","",Workspace!L22)</f>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="70">
         <f>=IF(Workspace!B22="","",Workspace!M22)</f>
       </c>
       <c r="K25">
@@ -6446,10 +7170,10 @@
       <c r="H26">
         <f>=IF(Workspace!B23="","",Workspace!B23)</f>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="70">
         <f>=IF(Workspace!B23="","",Workspace!L23)</f>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="70">
         <f>=IF(Workspace!B23="","",Workspace!M23)</f>
       </c>
       <c r="K26">
@@ -6463,10 +7187,10 @@
       <c r="H27">
         <f>=IF(Workspace!B24="","",Workspace!B24)</f>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="70">
         <f>=IF(Workspace!B24="","",Workspace!L24)</f>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="70">
         <f>=IF(Workspace!B24="","",Workspace!M24)</f>
       </c>
       <c r="K27">
@@ -6480,10 +7204,10 @@
       <c r="H28">
         <f>=IF(Workspace!B25="","",Workspace!B25)</f>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="70">
         <f>=IF(Workspace!B25="","",Workspace!L25)</f>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="70">
         <f>=IF(Workspace!B25="","",Workspace!M25)</f>
       </c>
       <c r="K28">
@@ -6497,10 +7221,10 @@
       <c r="H29">
         <f>=IF(Workspace!B26="","",Workspace!B26)</f>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="70">
         <f>=IF(Workspace!B26="","",Workspace!L26)</f>
       </c>
-      <c r="J29" s="37">
+      <c r="J29" s="70">
         <f>=IF(Workspace!B26="","",Workspace!M26)</f>
       </c>
       <c r="K29">
@@ -6514,10 +7238,10 @@
       <c r="H30">
         <f>=IF(Workspace!B27="","",Workspace!B27)</f>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="70">
         <f>=IF(Workspace!B27="","",Workspace!L27)</f>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="70">
         <f>=IF(Workspace!B27="","",Workspace!M27)</f>
       </c>
       <c r="K30">
@@ -6531,10 +7255,10 @@
       <c r="H31">
         <f>=IF(Workspace!B28="","",Workspace!B28)</f>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="70">
         <f>=IF(Workspace!B28="","",Workspace!L28)</f>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="70">
         <f>=IF(Workspace!B28="","",Workspace!M28)</f>
       </c>
       <c r="K31">
@@ -6548,10 +7272,10 @@
       <c r="H32">
         <f>=IF(Workspace!B29="","",Workspace!B29)</f>
       </c>
-      <c r="I32" s="37">
+      <c r="I32" s="70">
         <f>=IF(Workspace!B29="","",Workspace!L29)</f>
       </c>
-      <c r="J32" s="37">
+      <c r="J32" s="70">
         <f>=IF(Workspace!B29="","",Workspace!M29)</f>
       </c>
       <c r="K32">
@@ -6565,10 +7289,10 @@
       <c r="H33">
         <f>=IF(Workspace!B30="","",Workspace!B30)</f>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="70">
         <f>=IF(Workspace!B30="","",Workspace!L30)</f>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="70">
         <f>=IF(Workspace!B30="","",Workspace!M30)</f>
       </c>
       <c r="K33">
@@ -6582,10 +7306,10 @@
       <c r="H34">
         <f>=IF(Workspace!B31="","",Workspace!B31)</f>
       </c>
-      <c r="I34" s="37">
+      <c r="I34" s="70">
         <f>=IF(Workspace!B31="","",Workspace!L31)</f>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="70">
         <f>=IF(Workspace!B31="","",Workspace!M31)</f>
       </c>
       <c r="K34">
@@ -6596,8 +7320,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="C3:F3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="D12:E12"/>
   </mergeCells>
@@ -6645,6 +7373,55 @@
       <formula>$K5="Strategic Partner"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="expression" dxfId="28" priority="1">
+      <formula>$L$2="Proactively Defend"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="2">
+      <formula>$L$2="Defend"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="3">
+      <formula>$L$2="Protect"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="4">
+      <formula>$L$2="Respond"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="5">
+      <formula>$L$2="Identify"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="6">
+      <formula>$L$2="Monitor"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="7">
+      <formula>$L$2="Maintain"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="8">
+      <formula>$L$2="Connect"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="9">
+      <formula>$L$2="Commit"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="10">
+      <formula>$L$2="Cooperate"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="11">
+      <formula>$L$2="Collaborate"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="12">
+      <formula>$L$2="Valuable Relationship"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="13">
+      <formula>$L$2="High Value Relationship"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="14">
+      <formula>$L$2="Strategic Partner"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="H2">
+      <formula1>Workspace!$B$2:$B$31</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <drawing r:id="rIdDraw1"/>
@@ -6658,457 +7435,457 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="K1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="L1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="M1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="N1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="P1" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="Q1" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="R1" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="S1" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="U1" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="V1" t="s">
-        <v>110</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="J2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="K2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="L2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="M2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P2" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="S2" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="U2" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="V2" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="F3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L3" t="s">
+        <v>169</v>
+      </c>
+      <c r="M3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" t="s">
+        <v>211</v>
+      </c>
+      <c r="P3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="Q3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>227</v>
-      </c>
-      <c r="K3" t="s">
-        <v>256</v>
-      </c>
-      <c r="L3" t="s">
-        <v>162</v>
-      </c>
-      <c r="M3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N3" t="s">
-        <v>205</v>
-      </c>
-      <c r="P3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>115</v>
-      </c>
       <c r="R3" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="U3" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="V3" t="s">
-        <v>114</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" t="s">
+        <v>265</v>
+      </c>
+      <c r="K4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N4" t="s">
+        <v>266</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="S4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
-        <v>257</v>
-      </c>
-      <c r="K4" t="s">
-        <v>236</v>
-      </c>
-      <c r="L4" t="s">
-        <v>174</v>
-      </c>
-      <c r="N4" t="s">
-        <v>258</v>
-      </c>
-      <c r="P4" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>115</v>
-      </c>
-      <c r="R4" t="s">
-        <v>128</v>
-      </c>
-      <c r="S4" t="s">
-        <v>131</v>
-      </c>
       <c r="U4" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="V4" t="s">
-        <v>116</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="K5" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="P5" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="R5" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="S5" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="U5" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="V5" t="s">
-        <v>118</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="K6" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="R6" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="S6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="U6" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="V6" t="s">
-        <v>121</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="K7" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="U7" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="V7" t="s">
-        <v>123</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="K8" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="U8" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="V8" t="s">
-        <v>125</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="K9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="U9" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="V9" t="s">
-        <v>127</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="K10" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="U10" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="V10" t="s">
-        <v>130</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="U11" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="V11" t="s">
-        <v>132</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="U12" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="V12" t="s">
-        <v>134</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="U13" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="V13" t="s">
-        <v>136</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="U14" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="V14" t="s">
-        <v>138</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
